--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488033_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488033_PROCESSED_CHRONO.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.079</v>
+        <v>0.8663</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5835</v>
+        <v>2.0398</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5045</v>
+        <v>-1.1736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1911</v>
+        <v>-0.0771</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3155</v>
+        <v>0.8164</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1244</v>
+        <v>-0.8935</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9829</v>
+        <v>1.4755</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9829</v>
+        <v>2.9465</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.471</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-1.5525</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6674</v>
+        <v>-2.13</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1244</v>
+        <v>0.5775</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1982</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8968</v>
+        <v>-0.6323</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6006</v>
+        <v>-0.6605</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2962</v>
+        <v>0.0282</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2071</v>
+        <v>0.1881</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2071</v>
+        <v>-2.2261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3559</v>
+        <v>0.0385</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4452</v>
+        <v>1.6272</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0893</v>
+        <v>-1.5887</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0771</v>
+        <v>0.1911</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8164</v>
+        <v>0.3155</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8935</v>
+        <v>-0.1244</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4755</v>
+        <v>0.9829</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9465</v>
+        <v>0.9829</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.471</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5525</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.13</v>
+        <v>-0.6674</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5775</v>
+        <v>-0.1244</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5769</v>
+        <v>0.1982</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1428</v>
+        <v>0.8562</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2552</v>
+        <v>0.6443</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1124</v>
+        <v>0.2119</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1881</v>
+        <v>-1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2261</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2357</v>
+        <v>0.0242</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9306</v>
+        <v>-0.7268</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6949</v>
+        <v>0.751</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0015</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2342</v>
+        <v>0.0257</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.312</v>
+        <v>-0.1082</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.1339</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CASIN LORENTE</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2557</v>
+        <v>-0.1824</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6882</v>
+        <v>0.2077</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4325</v>
+        <v>-0.3901</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1316</v>
+        <v>-2.5642</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.409</v>
+        <v>-0.278</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2774</v>
+        <v>-2.2862</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0605</v>
+        <v>-0.8331</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0605</v>
+        <v>0.5252</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.3583</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1922</v>
+        <v>-1.7312</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4695</v>
+        <v>-0.8032</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2774</v>
+        <v>-0.928</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4372</v>
+        <v>1.0224</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2423</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1949</v>
+        <v>0.5148</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5613</v>
+        <v>-0.0282</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X6" t="n">
         <v>-0.5613</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>J. CASIN LORENTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.352</v>
+        <v>-0.2047</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1224</v>
+        <v>-0.6653</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4744</v>
+        <v>0.4606</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5642</v>
+        <v>-0.1316</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.278</v>
+        <v>-0.409</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2862</v>
+        <v>0.2774</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8331</v>
+        <v>0.0605</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5252</v>
+        <v>0.0605</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3583</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7312</v>
+        <v>-0.1922</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8032</v>
+        <v>-0.4695</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.928</v>
+        <v>0.2774</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8528</v>
+        <v>0.4882</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4223</v>
+        <v>0.2653</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4305</v>
+        <v>0.223</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0282</v>
+        <v>-0.5613</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>-0.5613</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5697</v>
+        <v>-1.0705</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6771</v>
+        <v>1.7832</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2468</v>
+        <v>-2.8537</v>
       </c>
       <c r="G8" t="n">
         <v>0.77</v>
@@ -1078,13 +1078,13 @@
         <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3288</v>
+        <v>-0.8296</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6647</v>
+        <v>-0.2293</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9935</v>
+        <v>-0.6004</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0109</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8657</v>
+        <v>-1.7358</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0132</v>
+        <v>-0.9113</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8526</v>
+        <v>-0.8245</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8309</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0437</v>
+        <v>0.0863</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2195</v>
+        <v>-4.4977</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6716</v>
+        <v>-3.7666</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5479</v>
+        <v>-0.7311</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0065</v>
+        <v>-1.5657</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.4769</v>
+        <v>-1.0911</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4705</v>
+        <v>-0.4746</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.163</v>
+        <v>0.2022</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2032</v>
+        <v>0.8411</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0402</v>
+        <v>-0.639</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8434</v>
+        <v>-1.7679</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.2737</v>
+        <v>-1.9322</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4303</v>
+        <v>0.1643</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1893</v>
+        <v>-4.1627</v>
       </c>
       <c r="R10" t="n">
         <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2222</v>
+        <v>-0.8287</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3192</v>
+        <v>-0.6762</v>
       </c>
       <c r="U10" t="n">
-        <v>0.097</v>
+        <v>-0.1525</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9908</v>
+        <v>0.8701</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9633</v>
+        <v>-4.9857</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4007</v>
+        <v>-3.0167</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5626</v>
+        <v>-1.9691</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5657</v>
+        <v>-3.0065</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0911</v>
+        <v>-3.4769</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4746</v>
+        <v>0.4705</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2022</v>
+        <v>-1.163</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8411</v>
+        <v>-1.2032</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.639</v>
+        <v>0.0402</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7679</v>
+        <v>-1.8434</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9322</v>
+        <v>-2.2737</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1643</v>
+        <v>0.4303</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1627</v>
+        <v>-1.1893</v>
       </c>
       <c r="R11" t="n">
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2944</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3103</v>
+        <v>-0.6643</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0159</v>
+        <v>-0.3241</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8701</v>
+        <v>-0.9908</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.9908</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0476</v>
+        <v>-5.8595</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.9301</v>
+        <v>-6.6015</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8824</v>
+        <v>0.7421</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5851</v>
@@ -1390,13 +1390,13 @@
         <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0936</v>
+        <v>0.0945</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2568</v>
+        <v>0.0717</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1632</v>
+        <v>0.0228</v>
       </c>
       <c r="V12" t="n">
         <v>-3.3779</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.049899999999999</v>
+        <v>-7.0997</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.035</v>
+        <v>-3.1972</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0148</v>
+        <v>-3.9025</v>
       </c>
       <c r="G13" t="n">
         <v>-2.52</v>
@@ -1468,13 +1468,13 @@
         <v>1.5858</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1145</v>
+        <v>-0.1643</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9984</v>
+        <v>-0.1605</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1161</v>
+        <v>-0.0038</v>
       </c>
       <c r="V13" t="n">
         <v>-2.8297</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.8231</v>
+        <v>-9.9924</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.4022</v>
+        <v>-5.768</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.4209</v>
+        <v>-4.2244</v>
       </c>
       <c r="G14" t="n">
         <v>-4.9577</v>
@@ -1546,13 +1546,13 @@
         <v>0.5947</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9518</v>
+        <v>-0.1211</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8736</v>
+        <v>-0.2394</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.1183</v>
       </c>
       <c r="V14" t="n">
         <v>-2.5349</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-34.7393</v>
+        <v>-33.4914</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.0354</v>
+        <v>-17.7875</v>
       </c>
       <c r="F15" t="n">
         <v>-15.704</v>
@@ -1597,7 +1597,7 @@
         <v>-7.2707</v>
       </c>
       <c r="J15" t="n">
-        <v>0.06589999999999963</v>
+        <v>0.06590000000000007</v>
       </c>
       <c r="K15" t="n">
         <v>6.8855</v>
@@ -1624,13 +1624,13 @@
         <v>12.8844</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2392</v>
+        <v>-0.9911</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.458</v>
+        <v>-1.21</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2188</v>
+        <v>0.2189</v>
       </c>
       <c r="V15" t="n">
         <v>-11.4826</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.5526</v>
+        <v>9.745900000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1931</v>
+        <v>6.4987</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3595</v>
+        <v>3.2471</v>
       </c>
       <c r="G16" t="n">
         <v>4.6891</v>
@@ -1702,13 +1702,13 @@
         <v>2.1805</v>
       </c>
       <c r="S16" t="n">
-        <v>0.707</v>
+        <v>0.9003</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1724</v>
+        <v>0.1332</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8794</v>
+        <v>0.767</v>
       </c>
       <c r="V16" t="n">
         <v>3.9583</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.003</v>
+        <v>7.1186</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0815</v>
+        <v>5.7758</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9216</v>
+        <v>1.3428</v>
       </c>
       <c r="G17" t="n">
         <v>4.6786</v>
@@ -1780,13 +1780,13 @@
         <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9599</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0696</v>
+        <v>-0.3752</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8903</v>
+        <v>-0.4691</v>
       </c>
       <c r="V17" t="n">
         <v>3.2843</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8259</v>
+        <v>6.8407</v>
       </c>
       <c r="E18" t="n">
-        <v>4.2558</v>
+        <v>4.7651</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5701</v>
+        <v>2.0755</v>
       </c>
       <c r="G18" t="n">
         <v>3.085</v>
@@ -1858,13 +1858,13 @@
         <v>2.7751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3384</v>
+        <v>0.6764</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2348</v>
+        <v>0.2746</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1036</v>
+        <v>0.4018</v>
       </c>
       <c r="V18" t="n">
         <v>2.4846</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.4022</v>
+        <v>5.3637</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1298</v>
+        <v>3.2317</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2724</v>
+        <v>2.132</v>
       </c>
       <c r="G19" t="n">
         <v>0.4432</v>
@@ -1936,13 +1936,13 @@
         <v>2.5769</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5011</v>
+        <v>0.4625</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.11</v>
+        <v>-0.0081</v>
       </c>
       <c r="U19" t="n">
-        <v>0.611</v>
+        <v>0.4707</v>
       </c>
       <c r="V19" t="n">
         <v>1.8811</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.3955</v>
+        <v>4.722</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9466</v>
+        <v>2.0484</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4489</v>
+        <v>2.6735</v>
       </c>
       <c r="G20" t="n">
         <v>4.8426</v>
@@ -2014,13 +2014,13 @@
         <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2599</v>
+        <v>-0.9334</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6864</v>
+        <v>-0.5845</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5735</v>
+        <v>-0.3489</v>
       </c>
       <c r="V20" t="n">
         <v>1.0109</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.7531</v>
+        <v>1.9587</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6636</v>
+        <v>0.543</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0896</v>
+        <v>1.4157</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6607</v>
@@ -2092,13 +2092,13 @@
         <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2949</v>
+        <v>1.5005</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6668</v>
+        <v>0.5462</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6281</v>
+        <v>0.9542</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0704</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>L. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6854</v>
+        <v>1.2124</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6762</v>
+        <v>0.0059</v>
       </c>
       <c r="F22" t="n">
-        <v>4.3617</v>
+        <v>1.2065</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8216</v>
+        <v>1.7547</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8252</v>
+        <v>0.7638</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0036</v>
+        <v>0.991</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5620000000000001</v>
+        <v>0.7262</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2623</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8243</v>
+        <v>0.0402</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3836</v>
+        <v>1.0285</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5629</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8207</v>
+        <v>0.9508</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5858</v>
+        <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7251</v>
+        <v>-1.0003</v>
       </c>
       <c r="T22" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.5221</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6589</v>
+        <v>-0.4782</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2666</v>
+        <v>-0.5331</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2666</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. PANOS HUERTAS</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8578</v>
+        <v>0.9449</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.096</v>
+        <v>-2.5744</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9538</v>
+        <v>3.5193</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7547</v>
+        <v>0.8216</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7638</v>
+        <v>0.8252</v>
       </c>
       <c r="I23" t="n">
-        <v>0.991</v>
+        <v>-0.0036</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7262</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.2623</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0402</v>
+        <v>-0.8243</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0285</v>
+        <v>1.3836</v>
       </c>
       <c r="N23" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.5629</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9508</v>
+        <v>0.8207</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9911</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3549</v>
+        <v>0.9846</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.624</v>
+        <v>0.1681</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7309</v>
+        <v>0.8165</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5331</v>
+        <v>-0.2666</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5331</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6282</v>
+        <v>0.6844</v>
       </c>
       <c r="E24" t="n">
         <v>0.4585</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1697</v>
+        <v>0.2259</v>
       </c>
       <c r="G24" t="n">
         <v>0.8514</v>
@@ -2326,13 +2326,13 @@
         <v>0.1982</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4214</v>
+        <v>-0.3652</v>
       </c>
       <c r="T24" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0483</v>
+        <v>-0.2696</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2976</v>
+        <v>-0.008</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3459</v>
+        <v>-0.2616</v>
       </c>
       <c r="G26" t="n">
         <v>-0.3981</v>
@@ -2482,13 +2482,13 @@
         <v>0.1982</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1516</v>
+        <v>-0.0697</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3671</v>
+        <v>0.0615</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.5134</v>
+        <v>-0.9832</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.1012</v>
+        <v>-1.7955</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5878</v>
+        <v>0.8124</v>
       </c>
       <c r="G27" t="n">
         <v>-2.2336</v>
@@ -2560,13 +2560,13 @@
         <v>1.3876</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5903</v>
+        <v>1.1206</v>
       </c>
       <c r="T27" t="n">
-        <v>0.202</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3883</v>
+        <v>0.6129</v>
       </c>
       <c r="V27" t="n">
         <v>-0.2666</v>
@@ -2593,10 +2593,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.1053</v>
+        <v>-2.9016</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.7517</v>
+        <v>-3.548</v>
       </c>
       <c r="F28" t="n">
         <v>0.6464</v>
@@ -2638,10 +2638,10 @@
         <v>0.3964</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.3964</v>
+        <v>-0.1927</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.4368</v>
+        <v>-0.233</v>
       </c>
       <c r="U28" t="n">
         <v>0.0403</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>34.7394</v>
+        <v>34.7396</v>
       </c>
       <c r="E29" t="n">
-        <v>15.7041</v>
+        <v>15.7039</v>
       </c>
       <c r="F29" t="n">
-        <v>19.0356</v>
+        <v>19.0355</v>
       </c>
       <c r="G29" t="n">
         <v>15.0712</v>
@@ -2716,13 +2716,13 @@
         <v>18.8312</v>
       </c>
       <c r="S29" t="n">
-        <v>2.239100000000001</v>
+        <v>2.239300000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.2191</v>
+        <v>-0.2188999999999999</v>
       </c>
       <c r="U29" t="n">
-        <v>2.458</v>
+        <v>2.4578</v>
       </c>
       <c r="V29" t="n">
         <v>11.4825</v>
